--- a/artfynd/A 62160-2023 artfynd.xlsx
+++ b/artfynd/A 62160-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128479865</v>
+        <v>128484842</v>
       </c>
       <c r="B2" t="n">
-        <v>92678</v>
+        <v>92754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548278</v>
+        <v>548262</v>
       </c>
       <c r="R2" t="n">
-        <v>6518362</v>
+        <v>6518361</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,6 +779,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128479865</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92770</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tjuttorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>548278</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6518362</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Suvi Sivula, Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62160-2023 artfynd.xlsx
+++ b/artfynd/A 62160-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128484842</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128479865</v>
       </c>
       <c r="B3" t="n">
-        <v>92770</v>
+        <v>92776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62160-2023 artfynd.xlsx
+++ b/artfynd/A 62160-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128484842</v>
       </c>
       <c r="B2" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128479865</v>
       </c>
       <c r="B3" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62160-2023 artfynd.xlsx
+++ b/artfynd/A 62160-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128484842</v>
       </c>
       <c r="B2" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128479865</v>
       </c>
       <c r="B3" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62160-2023 artfynd.xlsx
+++ b/artfynd/A 62160-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128484842</v>
       </c>
       <c r="B2" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128479865</v>
       </c>
       <c r="B3" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62160-2023 artfynd.xlsx
+++ b/artfynd/A 62160-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128484842</v>
       </c>
       <c r="B2" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128479865</v>
       </c>
       <c r="B3" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62160-2023 artfynd.xlsx
+++ b/artfynd/A 62160-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128484842</v>
       </c>
       <c r="B2" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128479865</v>
       </c>
       <c r="B3" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62160-2023 artfynd.xlsx
+++ b/artfynd/A 62160-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128484842</v>
       </c>
       <c r="B2" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128479865</v>
       </c>
       <c r="B3" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +795,12 @@
       <c r="E3" t="n">
         <v>5449</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 62160-2023 artfynd.xlsx
+++ b/artfynd/A 62160-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128484842</v>
       </c>
       <c r="B2" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128479865</v>
       </c>
       <c r="B3" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62160-2023 artfynd.xlsx
+++ b/artfynd/A 62160-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128484842</v>
       </c>
       <c r="B2" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128479865</v>
       </c>
       <c r="B3" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62160-2023 artfynd.xlsx
+++ b/artfynd/A 62160-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128484842</v>
+        <v>128501693</v>
       </c>
       <c r="B2" t="n">
-        <v>92818</v>
+        <v>91333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>2008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjuttorp, Ög</t>
+          <t>Norr om Tjuttorp, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548262</v>
+        <v>548270</v>
       </c>
       <c r="R2" t="n">
-        <v>6518361</v>
+        <v>6518373</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -743,19 +743,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Marika Sjödin</t>
+          <t>Marika Sjödin, Suvi Bergström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128479865</v>
+        <v>128501677</v>
       </c>
       <c r="B3" t="n">
-        <v>92835</v>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,25 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4361</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjuttorp, Ög</t>
+          <t>Norr om Tjuttorp, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548278</v>
+        <v>548279</v>
       </c>
       <c r="R3" t="n">
-        <v>6518362</v>
+        <v>6518393</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -841,19 +840,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,15 +857,1211 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Marika Sjödin</t>
+          <t>Marika Sjödin, Suvi Bergström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122745419</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Koloni- Ö, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>548281</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6518365</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128501706</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norr om Tjuttorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>548233</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6518408</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128501707</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norr om Tjuttorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>548242</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6518410</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Suvi Bergström, Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128501709</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norr om Tjuttorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>548281</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6518374</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128501710</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norr om Tjuttorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>548268</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6518375</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128501711</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norr om Tjuttorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>548271</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6518383</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128484842</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tjuttorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>548262</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6518361</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Suvi Bergström, Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122745420</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93300</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp agg.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Koloni- Ö, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>548286</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6518381</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122745417</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92651</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Koloni- Ö, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>548234</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6518410</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128479584</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tjuttorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>548230</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6518392</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Suvi Bergström, Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128484814</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tjuttorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>548295</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6518362</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Suvi Bergström, Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128501722</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norr om Tjuttorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>548299</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6518371</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62160-2023 artfynd.xlsx
+++ b/artfynd/A 62160-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501693</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501677</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122745419</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501706</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501707</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501709</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501710</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501711</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484842</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1656,6 +1706,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122745420</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122745417</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128479584</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1965,6 +2030,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484814</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2062,8 +2132,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501722</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>